--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_5.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_5.xlsx
@@ -463,127 +463,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[6, 9, 7, 9, 4]</t>
+          <t>[4, 9, 3, 9, 5]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9447248917358572</v>
+        <v>0.9728050704030994</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9447248917358572</v>
+        <v>0.9728050704030994</v>
       </c>
       <c r="E2" t="n">
-        <v>88.2</v>
+        <v>98.95</v>
       </c>
       <c r="F2" t="n">
-        <v>73.86999999999999</v>
+        <v>75.48999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[3, 0, 3, 8, 1]</t>
+          <t>[9, 8, 1, 2, 9]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9785171803297836</v>
+        <v>0.9532758692940119</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9785171803297836</v>
+        <v>0.9532758692940119</v>
       </c>
       <c r="E3" t="n">
-        <v>87.84999999999999</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>70.95</v>
+        <v>65.81999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[3, 0, 8, 2, 1]</t>
+          <t>[8, 9, 3, 2, 8]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9670798827992448</v>
+        <v>0.9520286776041799</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9670798827992448</v>
+        <v>0.9520286776041799</v>
       </c>
       <c r="E4" t="n">
-        <v>97.38999999999999</v>
+        <v>77.00999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>72.59999999999999</v>
+        <v>67.84999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[0, 1, 0, 6, 6]</t>
+          <t>[1, 5, 4, 3, 5]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9798499860963249</v>
+        <v>0.9802517879505562</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9798499860963249</v>
+        <v>0.9802517879505562</v>
       </c>
       <c r="E5" t="n">
-        <v>81.42</v>
+        <v>98.12</v>
       </c>
       <c r="F5" t="n">
-        <v>77.78999999999999</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[8, 9, 7, 8, 5]</t>
+          <t>[8, 7, 4, 6, 5]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9663900791910678</v>
+        <v>0.9429295808386047</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9663900791910678</v>
+        <v>0.9429295808386047</v>
       </c>
       <c r="E6" t="n">
-        <v>88.06</v>
+        <v>81.75</v>
       </c>
       <c r="F6" t="n">
-        <v>76.53999999999999</v>
+        <v>76.41999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[5, 0, 1, 2, 8]</t>
+          <t>[6, 5, 3, 1, 3]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -592,46 +592,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9700042271131528</v>
+        <v>0.9636891301722169</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9700042271131528</v>
+        <v>0.9636891301722169</v>
       </c>
       <c r="E7" t="n">
-        <v>93.85999999999999</v>
+        <v>89.64</v>
       </c>
       <c r="F7" t="n">
-        <v>70.22</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[8, 3, 8, 0, 3]</t>
+          <t>[4, 1, 4, 9, 8]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9798557562234551</v>
+        <v>0.9550696524572962</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9798557562234551</v>
+        <v>0.9550696524572962</v>
       </c>
       <c r="E8" t="n">
-        <v>84.66</v>
+        <v>95.87</v>
       </c>
       <c r="F8" t="n">
-        <v>66.48</v>
+        <v>71.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[0, 4, 2, 0, 8]</t>
+          <t>[6, 2, 1, 4, 9]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,46 +640,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9695660901608948</v>
+        <v>0.9610202097204802</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9695660901608948</v>
+        <v>0.9610202097204802</v>
       </c>
       <c r="E9" t="n">
-        <v>83.37</v>
+        <v>94.64</v>
       </c>
       <c r="F9" t="n">
-        <v>68.79000000000001</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[8, 2, 7, 5, 0]</t>
+          <t>[7, 9, 1, 7, 2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9773597505876743</v>
+        <v>0.9439507195304959</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9773597505876743</v>
+        <v>0.9439507195304959</v>
       </c>
       <c r="E10" t="n">
-        <v>90.17000000000002</v>
+        <v>79.22</v>
       </c>
       <c r="F10" t="n">
-        <v>75.56999999999999</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[5, 1, 4, 6, 4]</t>
+          <t>[6, 5, 8, 8, 8]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -688,70 +688,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9622150634241206</v>
+        <v>0.9400628170200757</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9622150634241206</v>
+        <v>0.9400628170200757</v>
       </c>
       <c r="E11" t="n">
-        <v>85.09</v>
+        <v>75.78999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>67.98</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[3, 1, 4, 8, 5]</t>
+          <t>[6, 9, 3, 9, 7]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9795968908531596</v>
+        <v>0.9361040810185622</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9795968908531596</v>
+        <v>0.9361040810185622</v>
       </c>
       <c r="E12" t="n">
-        <v>96.38999999999999</v>
+        <v>73.94</v>
       </c>
       <c r="F12" t="n">
-        <v>71.09999999999999</v>
+        <v>64.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[8, 3, 8, 7, 4]</t>
+          <t>[8, 2, 5, 6, 8]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9751811204736199</v>
+        <v>0.9508607489002037</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9751811204736199</v>
+        <v>0.9508607489002037</v>
       </c>
       <c r="E13" t="n">
-        <v>90.62</v>
+        <v>80.46000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>72.93000000000001</v>
+        <v>73.94999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[0, 1, 1, 3, 8]</t>
+          <t>[1, 0, 7, 0, 9]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,46 +760,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9699189136395464</v>
+        <v>0.9654580572775591</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9699189136395464</v>
+        <v>0.9654580572775591</v>
       </c>
       <c r="E14" t="n">
-        <v>74.67999999999999</v>
+        <v>92.44</v>
       </c>
       <c r="F14" t="n">
-        <v>56.95999999999999</v>
+        <v>60.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[8, 3, 9, 0, 9]</t>
+          <t>[3, 2, 3, 2, 7]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9782810253298415</v>
+        <v>0.981673030903348</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9782810253298415</v>
+        <v>0.981673030903348</v>
       </c>
       <c r="E15" t="n">
-        <v>97.17</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>73.14</v>
+        <v>78.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[5, 6, 1, 6, 4]</t>
+          <t>[4, 9, 9, 5, 4]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,46 +808,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9592360512917302</v>
+        <v>0.9413135076572277</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9592360512917302</v>
+        <v>0.9413135076572277</v>
       </c>
       <c r="E16" t="n">
-        <v>77.39</v>
+        <v>93.08000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>64.53</v>
+        <v>70.06999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[9, 9, 3, 8, 5]</t>
+          <t>[1, 9, 9, 5, 3]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9669306139341066</v>
+        <v>0.9703396029306859</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9669306139341066</v>
+        <v>0.9703396029306859</v>
       </c>
       <c r="E17" t="n">
-        <v>98.78</v>
+        <v>94.78999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>73.91</v>
+        <v>72.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[0, 6, 3, 8, 1]</t>
+          <t>[7, 9, 7, 5, 8]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,94 +856,94 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.960527188979008</v>
+        <v>0.9365287363811151</v>
       </c>
       <c r="D18" t="n">
-        <v>0.960527188979008</v>
+        <v>0.9365287363811151</v>
       </c>
       <c r="E18" t="n">
-        <v>71.38</v>
+        <v>70.22</v>
       </c>
       <c r="F18" t="n">
-        <v>59.14999999999999</v>
+        <v>75.23999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[5, 9, 0, 1, 8]</t>
+          <t>[0, 9, 3, 9, 8]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9762556589703508</v>
+        <v>0.9491437704463185</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9762556589703508</v>
+        <v>0.9491437704463185</v>
       </c>
       <c r="E19" t="n">
-        <v>90.66</v>
+        <v>96.19</v>
       </c>
       <c r="F19" t="n">
-        <v>73.13</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[2, 5, 3, 1, 9]</t>
+          <t>[8, 6, 3, 9, 9]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9647607831011797</v>
+        <v>0.9599508244753482</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9647607831011797</v>
+        <v>0.9599508244753482</v>
       </c>
       <c r="E20" t="n">
-        <v>88.40000000000001</v>
+        <v>90.83</v>
       </c>
       <c r="F20" t="n">
-        <v>64.41</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[7, 1, 1, 3, 4]</t>
+          <t>[0, 1, 5, 7, 4]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9816262880163558</v>
+        <v>0.9626141501636091</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9816262880163558</v>
+        <v>0.9626141501636091</v>
       </c>
       <c r="E21" t="n">
-        <v>97.88</v>
+        <v>92.12</v>
       </c>
       <c r="F21" t="n">
-        <v>77.22</v>
+        <v>68.11999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[6, 9, 5, 0, 8]</t>
+          <t>[7, 7, 3, 9, 0]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -952,190 +952,190 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9753245592828241</v>
+        <v>0.961113778447245</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9753245592828241</v>
+        <v>0.961113778447245</v>
       </c>
       <c r="E22" t="n">
-        <v>88.2</v>
+        <v>88.05</v>
       </c>
       <c r="F22" t="n">
-        <v>73.05</v>
+        <v>74.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[5, 6, 0, 3, 5]</t>
+          <t>[7, 0, 9, 3, 1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9771883659416157</v>
+        <v>0.9785437893648496</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9771883659416157</v>
+        <v>0.9785437893648496</v>
       </c>
       <c r="E23" t="n">
-        <v>81.99000000000001</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>73.33</v>
+        <v>71.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[3, 6, 5, 0, 9]</t>
+          <t>[3, 3, 2, 8, 0]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.96520314709896</v>
+        <v>0.9759129443875542</v>
       </c>
       <c r="D24" t="n">
-        <v>0.96520314709896</v>
+        <v>0.9759129443875542</v>
       </c>
       <c r="E24" t="n">
-        <v>95.95</v>
+        <v>93.98</v>
       </c>
       <c r="F24" t="n">
-        <v>78.84999999999999</v>
+        <v>68.75999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[6, 8, 5, 0, 8]</t>
+          <t>[4, 2, 4, 9, 5]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9762206678472279</v>
+        <v>0.9557623728589218</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9762206678472279</v>
+        <v>0.9557623728589218</v>
       </c>
       <c r="E25" t="n">
-        <v>81.02</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>69.73</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[0, 1, 0, 6, 9]</t>
+          <t>[2, 5, 3, 0, 8]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9799793078285464</v>
+        <v>0.9675827689398656</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9799793078285464</v>
+        <v>0.9675827689398656</v>
       </c>
       <c r="E26" t="n">
-        <v>88.93999999999998</v>
+        <v>83.91999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>79.02000000000001</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[4, 1, 8, 3, 8]</t>
+          <t>[7, 9, 3, 3, 1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9759103966784773</v>
+        <v>0.9557615562311401</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9759103966784773</v>
+        <v>0.9557615562311401</v>
       </c>
       <c r="E27" t="n">
-        <v>95.08</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>70.62</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[3, 8, 7, 1, 7]</t>
+          <t>[3, 2, 8, 5, 4]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9764108155386053</v>
+        <v>0.9594226106135521</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9764108155386053</v>
+        <v>0.9594226106135521</v>
       </c>
       <c r="E28" t="n">
-        <v>84.95</v>
+        <v>84.46000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>74.07000000000001</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[6, 0, 0, 9, 3]</t>
+          <t>[3, 3, 0, 3, 5]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9644139116902508</v>
+        <v>0.9835032421116006</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9644139116902508</v>
+        <v>0.9835032421116006</v>
       </c>
       <c r="E29" t="n">
-        <v>89.23999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="F29" t="n">
-        <v>79.31</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[9, 0, 5, 5, 2]</t>
+          <t>[5, 7, 3, 3, 2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1144,142 +1144,142 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9558683511515024</v>
+        <v>0.9590611775989611</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9558683511515024</v>
+        <v>0.9590611775989611</v>
       </c>
       <c r="E30" t="n">
-        <v>83.69</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>66.39</v>
+        <v>63.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[1, 1, 6, 7, 8]</t>
+          <t>[9, 1, 6, 3, 6]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9661485634679733</v>
+        <v>0.9492075496621798</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9661485634679733</v>
+        <v>0.9492075496621798</v>
       </c>
       <c r="E31" t="n">
-        <v>86.99000000000001</v>
+        <v>82.17</v>
       </c>
       <c r="F31" t="n">
-        <v>69.30000000000001</v>
+        <v>60.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[6, 1, 3, 3, 0]</t>
+          <t>[7, 9, 4, 2, 4]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9784565981606312</v>
+        <v>0.9508386936163594</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9784565981606312</v>
+        <v>0.9508386936163594</v>
       </c>
       <c r="E32" t="n">
-        <v>86.97</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>74.57000000000001</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[8, 1, 5, 3, 6]</t>
+          <t>[7, 9, 8, 3, 1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9827009079317547</v>
+        <v>0.9467489956991879</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9827009079317547</v>
+        <v>0.9467489956991879</v>
       </c>
       <c r="E33" t="n">
-        <v>99.64</v>
+        <v>94.55</v>
       </c>
       <c r="F33" t="n">
-        <v>79.74000000000001</v>
+        <v>77.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[5, 3, 8, 6, 0]</t>
+          <t>[3, 9, 5, 6, 1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.976040016290309</v>
+        <v>0.9742139710238664</v>
       </c>
       <c r="D34" t="n">
-        <v>0.976040016290309</v>
+        <v>0.9742139710238664</v>
       </c>
       <c r="E34" t="n">
-        <v>82.67</v>
+        <v>96.52</v>
       </c>
       <c r="F34" t="n">
-        <v>69.15000000000001</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[7, 8, 6, 0, 5]</t>
+          <t>[9, 7, 9, 0, 9]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9606672535798335</v>
+        <v>0.9706582851235618</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9606672535798335</v>
+        <v>0.9706582851235618</v>
       </c>
       <c r="E35" t="n">
-        <v>80.28999999999999</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>74.98</v>
+        <v>75.14000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[8, 8, 9, 8, 7]</t>
+          <t>[3, 1, 8, 1, 3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1288,334 +1288,334 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9658945865915116</v>
+        <v>0.976014143506973</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9658945865915116</v>
+        <v>0.976014143506973</v>
       </c>
       <c r="E36" t="n">
-        <v>89.67</v>
+        <v>98.47</v>
       </c>
       <c r="F36" t="n">
-        <v>67.67</v>
+        <v>69.16999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[0, 0, 8, 3, 7]</t>
+          <t>[3, 5, 0, 3, 1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.978367146300123</v>
+        <v>0.9796197519054379</v>
       </c>
       <c r="D37" t="n">
-        <v>0.978367146300123</v>
+        <v>0.9796197519054379</v>
       </c>
       <c r="E37" t="n">
-        <v>82.21000000000001</v>
+        <v>95</v>
       </c>
       <c r="F37" t="n">
-        <v>77.62</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[8, 6, 5, 1, 8]</t>
+          <t>[3, 4, 8, 0, 8]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.976806547332211</v>
+        <v>0.9601626432292559</v>
       </c>
       <c r="D38" t="n">
-        <v>0.976806547332211</v>
+        <v>0.9601626432292559</v>
       </c>
       <c r="E38" t="n">
-        <v>85.5</v>
+        <v>86.88</v>
       </c>
       <c r="F38" t="n">
-        <v>63.18000000000001</v>
+        <v>67.86999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[4, 8, 7, 5, 6]</t>
+          <t>[2, 3, 2, 5, 5]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9584749637781853</v>
+        <v>0.9829849418342691</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9584749637781853</v>
+        <v>0.9829849418342691</v>
       </c>
       <c r="E39" t="n">
-        <v>87.75</v>
+        <v>94.14</v>
       </c>
       <c r="F39" t="n">
-        <v>79.22</v>
+        <v>74.77999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[2, 3, 3, 8, 1]</t>
+          <t>[0, 3, 7, 9, 3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9806962586856911</v>
+        <v>0.974896499695625</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9806962586856911</v>
+        <v>0.974896499695625</v>
       </c>
       <c r="E40" t="n">
-        <v>97.69</v>
+        <v>91.94</v>
       </c>
       <c r="F40" t="n">
-        <v>72.89</v>
+        <v>69.86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[9, 8, 3, 0, 0]</t>
+          <t>[3, 5, 9, 3, 8]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9767321567024603</v>
+        <v>0.9720081846421933</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9767321567024603</v>
+        <v>0.9720081846421933</v>
       </c>
       <c r="E41" t="n">
-        <v>95.99000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>77.5</v>
+        <v>79.63999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[4, 1, 1, 5, 6]</t>
+          <t>[8, 1, 8, 5, 4]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9689803793484159</v>
+        <v>0.9498990137540001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9689803793484159</v>
+        <v>0.9498990137540001</v>
       </c>
       <c r="E42" t="n">
-        <v>93.86000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="F42" t="n">
-        <v>75.30000000000001</v>
+        <v>73.41999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[4, 1, 6, 1, 1]</t>
+          <t>[9, 3, 1, 2, 9]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9662567648782913</v>
+        <v>0.9727752475094109</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9662567648782913</v>
+        <v>0.9727752475094109</v>
       </c>
       <c r="E43" t="n">
-        <v>83.45</v>
+        <v>96.2</v>
       </c>
       <c r="F43" t="n">
-        <v>61.67999999999999</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[8, 6, 0, 3, 8]</t>
+          <t>[6, 8, 5, 6, 2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9770041271385523</v>
+        <v>0.943314404183189</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9770041271385523</v>
+        <v>0.943314404183189</v>
       </c>
       <c r="E44" t="n">
-        <v>82.13</v>
+        <v>82.87</v>
       </c>
       <c r="F44" t="n">
-        <v>70.68000000000001</v>
+        <v>71.69999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[0, 4, 0, 8, 7]</t>
+          <t>[3, 6, 5, 5, 9]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9645303516160941</v>
+        <v>0.9754065125992064</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9645303516160941</v>
+        <v>0.9754065125992064</v>
       </c>
       <c r="E45" t="n">
-        <v>73.44</v>
+        <v>93.06</v>
       </c>
       <c r="F45" t="n">
-        <v>69.27000000000001</v>
+        <v>76.69999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[8, 7, 7, 9, 6]</t>
+          <t>[3, 1, 3, 8, 5]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9677269641479579</v>
+        <v>0.9656566269835105</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9677269641479579</v>
+        <v>0.9656566269835105</v>
       </c>
       <c r="E46" t="n">
-        <v>87.52000000000001</v>
+        <v>89.81</v>
       </c>
       <c r="F46" t="n">
-        <v>78.06999999999999</v>
+        <v>73.88999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[8, 7, 3, 4, 8]</t>
+          <t>[9, 3, 5, 8, 6]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9753475609457516</v>
+        <v>0.9456206835298536</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9753475609457516</v>
+        <v>0.9456206835298536</v>
       </c>
       <c r="E47" t="n">
-        <v>97.44</v>
+        <v>75.42999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>80</v>
+        <v>65.17999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[8, 7, 9, 1, 6]</t>
+          <t>[6, 3, 9, 1, 6]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9558509787717379</v>
+        <v>0.9773147025583526</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9558509787717379</v>
+        <v>0.9773147025583526</v>
       </c>
       <c r="E48" t="n">
-        <v>90.33</v>
+        <v>99.12</v>
       </c>
       <c r="F48" t="n">
-        <v>76.34</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[8, 1, 1, 2, 6]</t>
+          <t>[1, 5, 3, 8, 6]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9781503011250507</v>
+        <v>0.9612161150753836</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9781503011250507</v>
+        <v>0.9612161150753836</v>
       </c>
       <c r="E49" t="n">
-        <v>99.33999999999999</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>70.25</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[5, 9, 1, 2, 8]</t>
+          <t>[1, 4, 2, 0, 3]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1624,40 +1624,40 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.959163450626177</v>
+        <v>0.9707720774528396</v>
       </c>
       <c r="D50" t="n">
-        <v>0.959163450626177</v>
+        <v>0.9707720774528396</v>
       </c>
       <c r="E50" t="n">
-        <v>87.63000000000001</v>
+        <v>96.56</v>
       </c>
       <c r="F50" t="n">
-        <v>61.37</v>
+        <v>61.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[0, 8, 8, 0, 6]</t>
+          <t>[6, 9, 6, 9, 6]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.980548365955731</v>
+        <v>0.959618966699167</v>
       </c>
       <c r="D51" t="n">
-        <v>0.980548365955731</v>
+        <v>0.959618966699167</v>
       </c>
       <c r="E51" t="n">
-        <v>95.11000000000001</v>
+        <v>99.09</v>
       </c>
       <c r="F51" t="n">
-        <v>77.72</v>
+        <v>77.7</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_5.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_5.xlsx
@@ -463,559 +463,559 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[8, 7, 8, 7, 1]</t>
+          <t>[5, 3, 5, 4, 6]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9232178928059355</v>
+        <v>0.9743983779070672</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9232178928059355</v>
+        <v>0.9743983779070672</v>
       </c>
       <c r="E2" t="n">
-        <v>93.96000000000001</v>
+        <v>103.1</v>
       </c>
       <c r="F2" t="n">
-        <v>53.74000000000001</v>
+        <v>95.25999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[6, 3, 7, 2, 3]</t>
+          <t>[7, 3, 3, 4, 7]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9425960982860901</v>
+        <v>0.9782541837323531</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9425960982860901</v>
+        <v>0.9782541837323531</v>
       </c>
       <c r="E3" t="n">
-        <v>84.12</v>
+        <v>113.87</v>
       </c>
       <c r="F3" t="n">
-        <v>71.92</v>
+        <v>93.55999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[2, 2, 8, 3, 4]</t>
+          <t>[6, 7, 9, 4, 8]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9512953975515079</v>
+        <v>0.9688501761708953</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9512953975515079</v>
+        <v>0.9688501761708953</v>
       </c>
       <c r="E4" t="n">
-        <v>75.17000000000002</v>
+        <v>116.31</v>
       </c>
       <c r="F4" t="n">
-        <v>77.17000000000002</v>
+        <v>92.22999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 5, 8]</t>
+          <t>[0, 3, 7, 3, 4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9559829954146469</v>
+        <v>0.992767272128475</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9559829954146469</v>
+        <v>0.992767272128475</v>
       </c>
       <c r="E5" t="n">
-        <v>95.44999999999999</v>
+        <v>111.95</v>
       </c>
       <c r="F5" t="n">
-        <v>61.8</v>
+        <v>86.75999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[8, 3, 5, 1, 1]</t>
+          <t>[1, 8, 5, 7, 3]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9473044798025624</v>
+        <v>0.9648272739805084</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9473044798025624</v>
+        <v>0.9648272739805084</v>
       </c>
       <c r="E6" t="n">
-        <v>87.75</v>
+        <v>88.67999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>64.29000000000001</v>
+        <v>81.53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[2, 6, 4, 2, 1]</t>
+          <t>[2, 7, 8, 7, 1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9567717151851639</v>
+        <v>0.9714341327915595</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9567717151851639</v>
+        <v>0.9714341327915595</v>
       </c>
       <c r="E7" t="n">
-        <v>91.22999999999999</v>
+        <v>105.78</v>
       </c>
       <c r="F7" t="n">
-        <v>77.33000000000001</v>
+        <v>92.43000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[8, 1, 5, 7, 2]</t>
+          <t>[1, 8, 5, 6, 4]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9406177893302964</v>
+        <v>0.9658725283654546</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9406177893302964</v>
+        <v>0.9658725283654546</v>
       </c>
       <c r="E8" t="n">
-        <v>92.16</v>
+        <v>97.72</v>
       </c>
       <c r="F8" t="n">
-        <v>62.05</v>
+        <v>86.15000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[2, 8, 7, 8, 2]</t>
+          <t>[3, 9, 7, 8, 0]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9334057838323369</v>
+        <v>0.967187697180605</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9334057838323369</v>
+        <v>0.967187697180605</v>
       </c>
       <c r="E9" t="n">
-        <v>86.40000000000001</v>
+        <v>110.04</v>
       </c>
       <c r="F9" t="n">
-        <v>65.81999999999999</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[6, 3, 9, 3, 8]</t>
+          <t>[6, 3, 7, 3, 9]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9387190370476244</v>
+        <v>0.9701027638955886</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9387190370476244</v>
+        <v>0.9701027638955886</v>
       </c>
       <c r="E10" t="n">
-        <v>87.35999999999999</v>
+        <v>114.19</v>
       </c>
       <c r="F10" t="n">
-        <v>75.25</v>
+        <v>90.50999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 4, 6]</t>
+          <t>[5, 5, 3, 4, 2]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9473380957958786</v>
+        <v>0.9898742990001831</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9473380957958786</v>
+        <v>0.9898742990001831</v>
       </c>
       <c r="E11" t="n">
-        <v>77.45</v>
+        <v>107.49</v>
       </c>
       <c r="F11" t="n">
-        <v>73.40000000000001</v>
+        <v>98.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[3, 8, 1, 7, 9]</t>
+          <t>[1, 7, 1, 7, 0]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9418503249667164</v>
+        <v>0.9789142034185532</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9418503249667164</v>
+        <v>0.9789142034185532</v>
       </c>
       <c r="E12" t="n">
-        <v>90.16999999999999</v>
+        <v>113.34</v>
       </c>
       <c r="F12" t="n">
-        <v>64.34999999999999</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[1, 1, 4, 4, 1]</t>
+          <t>[4, 6, 7, 0, 4]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9804373990583871</v>
+        <v>0.9698516258302147</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9804373990583871</v>
+        <v>0.9698516258302147</v>
       </c>
       <c r="E13" t="n">
-        <v>87.90000000000001</v>
+        <v>109.58</v>
       </c>
       <c r="F13" t="n">
-        <v>69.22</v>
+        <v>83.57999999999998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[4, 7, 8, 7, 4]</t>
+          <t>[5, 6, 7, 8, 9]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9355528906908812</v>
+        <v>0.9671665180443074</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9355528906908812</v>
+        <v>0.9671665180443074</v>
       </c>
       <c r="E14" t="n">
-        <v>98.12</v>
+        <v>112.71</v>
       </c>
       <c r="F14" t="n">
-        <v>79.33</v>
+        <v>99.05000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[3, 2, 1, 1, 4]</t>
+          <t>[7, 8, 8, 8, 1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9665473270520143</v>
+        <v>0.9638339807673932</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9665473270520143</v>
+        <v>0.9638339807673932</v>
       </c>
       <c r="E15" t="n">
-        <v>73.62</v>
+        <v>117.89</v>
       </c>
       <c r="F15" t="n">
-        <v>67.61000000000001</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[5, 8, 4, 5, 4]</t>
+          <t>[6, 1, 3, 5, 0]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9347477262388043</v>
+        <v>0.9568148297769415</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9347477262388043</v>
+        <v>0.9568148297769415</v>
       </c>
       <c r="E16" t="n">
-        <v>89.63</v>
+        <v>105.44</v>
       </c>
       <c r="F16" t="n">
-        <v>74.98</v>
+        <v>87.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[5, 3, 8, 3, 9]</t>
+          <t>[3, 7, 2, 1, 9]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.939220009414647</v>
+        <v>0.958123721775492</v>
       </c>
       <c r="D17" t="n">
-        <v>0.939220009414647</v>
+        <v>0.958123721775492</v>
       </c>
       <c r="E17" t="n">
-        <v>91.88999999999999</v>
+        <v>101.72</v>
       </c>
       <c r="F17" t="n">
-        <v>78.42</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[4, 6, 6, 4, 6]</t>
+          <t>[7, 6, 5, 1, 1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9653839622590772</v>
+        <v>0.9899656202075805</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9653839622590772</v>
+        <v>0.9899656202075805</v>
       </c>
       <c r="E18" t="n">
-        <v>99.02000000000001</v>
+        <v>99.41</v>
       </c>
       <c r="F18" t="n">
-        <v>79.70000000000002</v>
+        <v>97.45000000000002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[9, 1, 1, 6, 6]</t>
+          <t>[9, 9, 7, 3, 6]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9533444432747336</v>
+        <v>0.9425237658405942</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9533444432747336</v>
+        <v>0.9425237658405942</v>
       </c>
       <c r="E19" t="n">
-        <v>88.19</v>
+        <v>99.53</v>
       </c>
       <c r="F19" t="n">
-        <v>57.79000000000001</v>
+        <v>81.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[7, 8, 9, 9, 9]</t>
+          <t>[2, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.918017686358008</v>
+        <v>0.9736052408406994</v>
       </c>
       <c r="D20" t="n">
-        <v>0.918017686358008</v>
+        <v>0.9736052408406994</v>
       </c>
       <c r="E20" t="n">
-        <v>99.62</v>
+        <v>98.27999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>67.77</v>
+        <v>74.48999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[4, 7, 2, 4, 8]</t>
+          <t>[7, 7, 4, 5, 1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9709801669782675</v>
+        <v>0.9711183450561013</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9709801669782675</v>
+        <v>0.9711183450561013</v>
       </c>
       <c r="E21" t="n">
-        <v>99.84999999999999</v>
+        <v>97.39</v>
       </c>
       <c r="F21" t="n">
-        <v>78.78</v>
+        <v>92.96000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[1, 0, 4, 9, 8]</t>
+          <t>[2, 3, 6, 1, 5]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9578608264065848</v>
+        <v>0.978552960159834</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9578608264065848</v>
+        <v>0.978552960159834</v>
       </c>
       <c r="E22" t="n">
-        <v>90.12</v>
+        <v>113.09</v>
       </c>
       <c r="F22" t="n">
-        <v>69.63</v>
+        <v>99.18000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[3, 1, 2, 7, 2]</t>
+          <t>[9, 3, 5, 7, 7]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9563487041866157</v>
+        <v>0.9668418062317552</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9563487041866157</v>
+        <v>0.9668418062317552</v>
       </c>
       <c r="E23" t="n">
-        <v>80.55</v>
+        <v>96.58</v>
       </c>
       <c r="F23" t="n">
-        <v>67.06</v>
+        <v>87.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[2, 0, 6, 9, 4]</t>
+          <t>[1, 1, 9, 9, 1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9510155933938498</v>
+        <v>0.9691542957333039</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9510155933938498</v>
+        <v>0.9691542957333039</v>
       </c>
       <c r="E24" t="n">
-        <v>88.99000000000001</v>
+        <v>103.26</v>
       </c>
       <c r="F24" t="n">
-        <v>74.77</v>
+        <v>92.72999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[7, 8, 3, 2, 4]</t>
+          <t>[7, 3, 7, 4, 4]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1024,640 +1024,640 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9426187845911466</v>
+        <v>0.947049606349985</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9426187845911466</v>
+        <v>0.947049606349985</v>
       </c>
       <c r="E25" t="n">
-        <v>81.55000000000001</v>
+        <v>75.31</v>
       </c>
       <c r="F25" t="n">
-        <v>71.13</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[6, 9, 3, 1, 5]</t>
+          <t>[4, 4, 2, 1, 8]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.947868153283048</v>
+        <v>0.9738605254014545</v>
       </c>
       <c r="D26" t="n">
-        <v>0.947868153283048</v>
+        <v>0.9738605254014545</v>
       </c>
       <c r="E26" t="n">
-        <v>92.33000000000001</v>
+        <v>106.44</v>
       </c>
       <c r="F26" t="n">
-        <v>69.23999999999999</v>
+        <v>88.06999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[4, 2, 4, 0, 6]</t>
+          <t>[3, 4, 1, 3, 6]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9593753431906168</v>
+        <v>0.9754017591902626</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9593753431906168</v>
+        <v>0.9754017591902626</v>
       </c>
       <c r="E27" t="n">
-        <v>81.55</v>
+        <v>98.03999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>75.50999999999999</v>
+        <v>78.21000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[8, 1, 1, 3, 9]</t>
+          <t>[7, 7, 1, 3, 4]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.957886798817808</v>
+        <v>0.992439109841606</v>
       </c>
       <c r="D28" t="n">
-        <v>0.957886798817808</v>
+        <v>0.992439109841606</v>
       </c>
       <c r="E28" t="n">
-        <v>84.97</v>
+        <v>115.33</v>
       </c>
       <c r="F28" t="n">
-        <v>64.34999999999999</v>
+        <v>99.07000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[0, 8, 3, 1, 4]</t>
+          <t>[9, 2, 3, 6, 4]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9594569506101309</v>
+        <v>0.9701634197779562</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9594569506101309</v>
+        <v>0.9701634197779562</v>
       </c>
       <c r="E29" t="n">
-        <v>85.20000000000002</v>
+        <v>104.61</v>
       </c>
       <c r="F29" t="n">
-        <v>72.06</v>
+        <v>82.06999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[3, 2, 8, 1, 9]</t>
+          <t>[5, 1, 3, 6, 0]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9667338035178102</v>
+        <v>0.9746290026671346</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9667338035178102</v>
+        <v>0.9746290026671346</v>
       </c>
       <c r="E30" t="n">
-        <v>99.41</v>
+        <v>115.8</v>
       </c>
       <c r="F30" t="n">
-        <v>79.72999999999999</v>
+        <v>98.41999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[8, 8, 5, 1, 6]</t>
+          <t>[6, 0, 8, 3, 9]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9389701664824294</v>
+        <v>0.9533579022383519</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9389701664824294</v>
+        <v>0.9533579022383519</v>
       </c>
       <c r="E31" t="n">
-        <v>93.65000000000001</v>
+        <v>114.26</v>
       </c>
       <c r="F31" t="n">
-        <v>62.15</v>
+        <v>86.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[5, 2, 3, 1, 1]</t>
+          <t>[8, 2, 5, 7, 8]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9600818399195229</v>
+        <v>0.9432108005664485</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9600818399195229</v>
+        <v>0.9432108005664485</v>
       </c>
       <c r="E32" t="n">
-        <v>99.45999999999999</v>
+        <v>86.52</v>
       </c>
       <c r="F32" t="n">
-        <v>76.15000000000001</v>
+        <v>71.07000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[2, 2, 5, 3, 7]</t>
+          <t>[3, 6, 9, 7, 9]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9518990227730294</v>
+        <v>0.96406053362297</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9518990227730294</v>
+        <v>0.96406053362297</v>
       </c>
       <c r="E33" t="n">
-        <v>87.86000000000001</v>
+        <v>95.31</v>
       </c>
       <c r="F33" t="n">
-        <v>72.85000000000001</v>
+        <v>78.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[2, 7, 8, 7, 0]</t>
+          <t>[6, 7, 1, 1, 4]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9345847454172387</v>
+        <v>0.958937318815045</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9345847454172387</v>
+        <v>0.958937318815045</v>
       </c>
       <c r="E34" t="n">
-        <v>97.72</v>
+        <v>111.88</v>
       </c>
       <c r="F34" t="n">
-        <v>63.23</v>
+        <v>95.21000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[0, 6, 1, 3, 9]</t>
+          <t>[0, 8, 7, 2, 1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9578958947540487</v>
+        <v>0.9729446324561078</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9578958947540487</v>
+        <v>0.9729446324561078</v>
       </c>
       <c r="E35" t="n">
-        <v>92.69</v>
+        <v>116.24</v>
       </c>
       <c r="F35" t="n">
-        <v>70.42</v>
+        <v>97.12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[0, 6, 6, 5, 2]</t>
+          <t>[6, 4, 7, 0, 4]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9448763043255003</v>
+        <v>0.9778277450032047</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9448763043255003</v>
+        <v>0.9778277450032047</v>
       </c>
       <c r="E36" t="n">
-        <v>97.45999999999999</v>
+        <v>119.94</v>
       </c>
       <c r="F36" t="n">
-        <v>70.74000000000001</v>
+        <v>94.57999999999998</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[6, 9, 6, 3, 9]</t>
+          <t>[4, 3, 5, 8, 5]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9335306524885265</v>
+        <v>0.9907738230222226</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9335306524885265</v>
+        <v>0.9907738230222226</v>
       </c>
       <c r="E37" t="n">
-        <v>92.32999999999998</v>
+        <v>111.64</v>
       </c>
       <c r="F37" t="n">
-        <v>71.92</v>
+        <v>96.22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[9, 9, 2, 5, 7]</t>
+          <t>[5, 9, 5, 3, 8]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9328463930290452</v>
+        <v>0.9871748674714552</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9328463930290452</v>
+        <v>0.9871748674714552</v>
       </c>
       <c r="E38" t="n">
-        <v>98.48999999999998</v>
+        <v>108.1</v>
       </c>
       <c r="F38" t="n">
-        <v>70.23</v>
+        <v>96.03999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[4, 1, 7, 8, 4]</t>
+          <t>[0, 1, 3, 5, 2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.946389487844005</v>
+        <v>0.9769179972525125</v>
       </c>
       <c r="D39" t="n">
-        <v>0.946389487844005</v>
+        <v>0.9769179972525125</v>
       </c>
       <c r="E39" t="n">
-        <v>80.21000000000001</v>
+        <v>117.39</v>
       </c>
       <c r="F39" t="n">
-        <v>63.4</v>
+        <v>97.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[8, 3, 3, 5, 9]</t>
+          <t>[7, 1, 5, 8, 0]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9405740157451857</v>
+        <v>0.9746413379036526</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9405740157451857</v>
+        <v>0.9746413379036526</v>
       </c>
       <c r="E40" t="n">
-        <v>91.89000000000001</v>
+        <v>108.38</v>
       </c>
       <c r="F40" t="n">
-        <v>78.42</v>
+        <v>94.68000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[5, 3, 2, 8, 3]</t>
+          <t>[5, 1, 9, 3, 7]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.944315775388918</v>
+        <v>0.9669377267192327</v>
       </c>
       <c r="D41" t="n">
-        <v>0.944315775388918</v>
+        <v>0.9669377267192327</v>
       </c>
       <c r="E41" t="n">
-        <v>86.17999999999999</v>
+        <v>105.96</v>
       </c>
       <c r="F41" t="n">
-        <v>78.61</v>
+        <v>91.42999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[2, 2, 8, 7, 1]</t>
+          <t>[1, 6, 5, 6, 3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9494217078601451</v>
+        <v>0.989901922187825</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9494217078601451</v>
+        <v>0.989901922187825</v>
       </c>
       <c r="E42" t="n">
-        <v>99.29000000000001</v>
+        <v>108.22</v>
       </c>
       <c r="F42" t="n">
-        <v>71.64000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[7, 6, 2, 6, 8]</t>
+          <t>[7, 3, 7, 3, 4]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9361188553612402</v>
+        <v>0.9916443491780622</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9361188553612402</v>
+        <v>0.9916443491780622</v>
       </c>
       <c r="E43" t="n">
-        <v>90.41</v>
+        <v>117.12</v>
       </c>
       <c r="F43" t="n">
-        <v>61.5</v>
+        <v>93.58000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[7, 2, 0, 3, 9]</t>
+          <t>[9, 7, 3, 4, 5]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9547021404245685</v>
+        <v>0.9495690255351407</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9547021404245685</v>
+        <v>0.9495690255351407</v>
       </c>
       <c r="E44" t="n">
-        <v>93.93000000000001</v>
+        <v>101.44</v>
       </c>
       <c r="F44" t="n">
-        <v>73.84</v>
+        <v>95.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[1, 8, 3, 4, 2]</t>
+          <t>[3, 2, 3, 4, 5]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9523358390370444</v>
+        <v>0.9760982637295897</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9523358390370444</v>
+        <v>0.9760982637295897</v>
       </c>
       <c r="E45" t="n">
-        <v>76.35000000000001</v>
+        <v>109.02</v>
       </c>
       <c r="F45" t="n">
-        <v>71.13</v>
+        <v>93.53999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[2, 4, 7, 1, 4]</t>
+          <t>[3, 4, 6, 9, 0]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9541902650850846</v>
+        <v>0.9662345135450295</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9541902650850846</v>
+        <v>0.9662345135450295</v>
       </c>
       <c r="E46" t="n">
-        <v>76.3</v>
+        <v>108.29</v>
       </c>
       <c r="F46" t="n">
-        <v>65.92000000000002</v>
+        <v>83.38999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[6, 2, 0, 6, 1]</t>
+          <t>[1, 7, 9, 5, 4]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9537101271261245</v>
+        <v>0.971694779045611</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9537101271261245</v>
+        <v>0.971694779045611</v>
       </c>
       <c r="E47" t="n">
-        <v>90.15000000000001</v>
+        <v>106.26</v>
       </c>
       <c r="F47" t="n">
-        <v>64.95</v>
+        <v>97.54000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[2, 8, 5, 2, 9]</t>
+          <t>[4, 7, 3, 1, 0]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9443181890068494</v>
+        <v>0.973042648375998</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9443181890068494</v>
+        <v>0.973042648375998</v>
       </c>
       <c r="E48" t="n">
-        <v>90.31</v>
+        <v>101.03</v>
       </c>
       <c r="F48" t="n">
-        <v>73.94000000000001</v>
+        <v>80.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[3, 0, 5, 4, 6]</t>
+          <t>[0, 7, 5, 6, 7]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.953802959320325</v>
+        <v>0.9916807893622301</v>
       </c>
       <c r="D49" t="n">
-        <v>0.953802959320325</v>
+        <v>0.9916807893622301</v>
       </c>
       <c r="E49" t="n">
-        <v>92.56</v>
+        <v>105.34</v>
       </c>
       <c r="F49" t="n">
-        <v>76.95000000000002</v>
+        <v>95.33999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[6, 2, 7, 0, 2]</t>
+          <t>[5, 7, 7, 9, 3]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.947853802345169</v>
+        <v>0.9438376574923658</v>
       </c>
       <c r="D50" t="n">
-        <v>0.947853802345169</v>
+        <v>0.9438376574923658</v>
       </c>
       <c r="E50" t="n">
-        <v>91.38999999999999</v>
+        <v>103.08</v>
       </c>
       <c r="F50" t="n">
-        <v>68.37</v>
+        <v>87.46000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[1, 8, 1, 9, 0]</t>
+          <t>[8, 7, 1, 5, 9]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9480710483512178</v>
+        <v>0.9684210436607379</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9480710483512178</v>
+        <v>0.9684210436607379</v>
       </c>
       <c r="E51" t="n">
-        <v>93.03</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>63.03999999999999</v>
+        <v>82.45999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_5.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_5.xlsx
@@ -463,583 +463,583 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 4, 6]</t>
+          <t>[5, 9, 2, 8, 8]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 2]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9743983779070672</v>
+        <v>0.9696593747154904</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9743983779070672</v>
+        <v>0.9696593747154904</v>
       </c>
       <c r="E2" t="n">
-        <v>103.1</v>
+        <v>118.02</v>
       </c>
       <c r="F2" t="n">
-        <v>95.25999999999999</v>
+        <v>95.43000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[7, 3, 3, 4, 7]</t>
+          <t>[3, 7, 2, 0, 8]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[3, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9782541837323531</v>
+        <v>0.9596172402235192</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9782541837323531</v>
+        <v>0.9596172402235192</v>
       </c>
       <c r="E3" t="n">
-        <v>113.87</v>
+        <v>108.46</v>
       </c>
       <c r="F3" t="n">
-        <v>93.55999999999999</v>
+        <v>79.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[6, 7, 9, 4, 8]</t>
+          <t>[1, 8, 5, 9, 5]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9688501761708953</v>
+        <v>0.9717191045354391</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9688501761708953</v>
+        <v>0.9717191045354391</v>
       </c>
       <c r="E4" t="n">
-        <v>116.31</v>
+        <v>109.86</v>
       </c>
       <c r="F4" t="n">
-        <v>92.22999999999999</v>
+        <v>90.17000000000002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[0, 3, 7, 3, 4]</t>
+          <t>[8, 2, 7, 0, 8]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.992767272128475</v>
+        <v>0.9756078237996924</v>
       </c>
       <c r="D5" t="n">
-        <v>0.992767272128475</v>
+        <v>0.9756078237996924</v>
       </c>
       <c r="E5" t="n">
-        <v>111.95</v>
+        <v>100.89</v>
       </c>
       <c r="F5" t="n">
-        <v>86.75999999999999</v>
+        <v>80.48999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[1, 8, 5, 7, 3]</t>
+          <t>[1, 5, 5, 9, 9]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9648272739805084</v>
+        <v>0.9685857042311513</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9648272739805084</v>
+        <v>0.9685857042311513</v>
       </c>
       <c r="E6" t="n">
-        <v>88.67999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="F6" t="n">
-        <v>81.53</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[2, 7, 8, 7, 1]</t>
+          <t>[1, 0, 2, 3, 0]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9714341327915595</v>
+        <v>0.9631429052159698</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9714341327915595</v>
+        <v>0.9631429052159698</v>
       </c>
       <c r="E7" t="n">
-        <v>105.78</v>
+        <v>103.52</v>
       </c>
       <c r="F7" t="n">
-        <v>92.43000000000001</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[1, 8, 5, 6, 4]</t>
+          <t>[8, 6, 3, 3, 5]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9658725283654546</v>
+        <v>0.9647123846630054</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9658725283654546</v>
+        <v>0.9647123846630054</v>
       </c>
       <c r="E8" t="n">
-        <v>97.72</v>
+        <v>115.78</v>
       </c>
       <c r="F8" t="n">
-        <v>86.15000000000001</v>
+        <v>71.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[3, 9, 7, 8, 0]</t>
+          <t>[2, 0, 8, 3, 2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.967187697180605</v>
+        <v>0.9552275565288609</v>
       </c>
       <c r="D9" t="n">
-        <v>0.967187697180605</v>
+        <v>0.9552275565288609</v>
       </c>
       <c r="E9" t="n">
-        <v>110.04</v>
+        <v>102.46</v>
       </c>
       <c r="F9" t="n">
-        <v>84.15000000000001</v>
+        <v>60.42000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[6, 3, 7, 3, 9]</t>
+          <t>[4, 7, 3, 3, 7]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9701027638955886</v>
+        <v>0.9438236522729169</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9701027638955886</v>
+        <v>0.9438236522729169</v>
       </c>
       <c r="E10" t="n">
-        <v>114.19</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>90.50999999999999</v>
+        <v>67.68000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 4, 2]</t>
+          <t>[8, 0, 7, 3, 6]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9898742990001831</v>
+        <v>0.9746237651728776</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9898742990001831</v>
+        <v>0.9746237651728776</v>
       </c>
       <c r="E11" t="n">
-        <v>107.49</v>
+        <v>105.75</v>
       </c>
       <c r="F11" t="n">
-        <v>98.09</v>
+        <v>82.00000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[1, 7, 1, 7, 0]</t>
+          <t>[8, 5, 4, 7, 1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9789142034185532</v>
+        <v>0.9638139219037047</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9789142034185532</v>
+        <v>0.9638139219037047</v>
       </c>
       <c r="E12" t="n">
-        <v>113.34</v>
+        <v>99.46000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>97.75</v>
+        <v>82.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[4, 6, 7, 0, 4]</t>
+          <t>[4, 3, 7, 7, 7]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9698516258302147</v>
+        <v>0.9651912546045742</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9698516258302147</v>
+        <v>0.9651912546045742</v>
       </c>
       <c r="E13" t="n">
-        <v>109.58</v>
+        <v>112.1</v>
       </c>
       <c r="F13" t="n">
-        <v>83.57999999999998</v>
+        <v>84.58000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[5, 6, 7, 8, 9]</t>
+          <t>[5, 2, 6, 6, 0]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9671665180443074</v>
+        <v>0.9443595052918891</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9671665180443074</v>
+        <v>0.9443595052918891</v>
       </c>
       <c r="E14" t="n">
-        <v>112.71</v>
+        <v>97.77</v>
       </c>
       <c r="F14" t="n">
-        <v>99.05000000000001</v>
+        <v>60.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[7, 8, 8, 8, 1]</t>
+          <t>[0, 1, 7, 9, 7]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9638339807673932</v>
+        <v>0.9706006784997802</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9638339807673932</v>
+        <v>0.9706006784997802</v>
       </c>
       <c r="E15" t="n">
-        <v>117.89</v>
+        <v>105.35</v>
       </c>
       <c r="F15" t="n">
-        <v>96.11</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[6, 1, 3, 5, 0]</t>
+          <t>[7, 7, 2, 6, 1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9568148297769415</v>
+        <v>0.9686560350500464</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9568148297769415</v>
+        <v>0.9686560350500464</v>
       </c>
       <c r="E16" t="n">
-        <v>105.44</v>
+        <v>109.17</v>
       </c>
       <c r="F16" t="n">
-        <v>87.42</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[3, 7, 2, 1, 9]</t>
+          <t>[7, 9, 6, 8, 1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.958123721775492</v>
+        <v>0.9327544601117467</v>
       </c>
       <c r="D17" t="n">
-        <v>0.958123721775492</v>
+        <v>0.9327544601117467</v>
       </c>
       <c r="E17" t="n">
-        <v>101.72</v>
+        <v>85.25999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>86.3</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[7, 6, 5, 1, 1]</t>
+          <t>[0, 3, 7, 3, 5]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9899656202075805</v>
+        <v>0.957140800735636</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9899656202075805</v>
+        <v>0.957140800735636</v>
       </c>
       <c r="E18" t="n">
-        <v>99.41</v>
+        <v>108.18</v>
       </c>
       <c r="F18" t="n">
-        <v>97.45000000000002</v>
+        <v>75.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[9, 9, 7, 3, 6]</t>
+          <t>[1, 4, 9, 1, 2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9425237658405942</v>
+        <v>0.9697383681307867</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9425237658405942</v>
+        <v>0.9697383681307867</v>
       </c>
       <c r="E19" t="n">
-        <v>99.53</v>
+        <v>119.19</v>
       </c>
       <c r="F19" t="n">
-        <v>81.08</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[2, 3, 3, 3, 3]</t>
+          <t>[2, 4, 9, 5, 5]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9736052408406994</v>
+        <v>0.9470457162395585</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9736052408406994</v>
+        <v>0.9470457162395585</v>
       </c>
       <c r="E20" t="n">
-        <v>98.27999999999999</v>
+        <v>109.08</v>
       </c>
       <c r="F20" t="n">
-        <v>74.48999999999999</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[7, 7, 4, 5, 1]</t>
+          <t>[7, 8, 2, 1, 5]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 2]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9711183450561013</v>
+        <v>0.9890174238296343</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9711183450561013</v>
+        <v>0.9890174238296343</v>
       </c>
       <c r="E21" t="n">
-        <v>97.39</v>
+        <v>116.54</v>
       </c>
       <c r="F21" t="n">
-        <v>92.96000000000001</v>
+        <v>92.33000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[2, 3, 6, 1, 5]</t>
+          <t>[5, 7, 6, 8, 9]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.978552960159834</v>
+        <v>0.9685234362183981</v>
       </c>
       <c r="D22" t="n">
-        <v>0.978552960159834</v>
+        <v>0.9685234362183981</v>
       </c>
       <c r="E22" t="n">
-        <v>113.09</v>
+        <v>110.62</v>
       </c>
       <c r="F22" t="n">
-        <v>99.18000000000001</v>
+        <v>96.84999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[9, 3, 5, 7, 7]</t>
+          <t>[9, 8, 5, 4, 0]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9668418062317552</v>
+        <v>0.9629868075365517</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9668418062317552</v>
+        <v>0.9629868075365517</v>
       </c>
       <c r="E23" t="n">
-        <v>96.58</v>
+        <v>110.15</v>
       </c>
       <c r="F23" t="n">
-        <v>87.42</v>
+        <v>89.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[1, 1, 9, 9, 1]</t>
+          <t>[5, 9, 5, 8, 0]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9691542957333039</v>
+        <v>0.9339336606277139</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9691542957333039</v>
+        <v>0.9339336606277139</v>
       </c>
       <c r="E24" t="n">
-        <v>103.26</v>
+        <v>82.72</v>
       </c>
       <c r="F24" t="n">
-        <v>92.72999999999999</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[7, 3, 7, 4, 4]</t>
+          <t>[0, 6, 8, 1, 4]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.947049606349985</v>
+        <v>0.9723817093830021</v>
       </c>
       <c r="D25" t="n">
-        <v>0.947049606349985</v>
+        <v>0.9723817093830021</v>
       </c>
       <c r="E25" t="n">
-        <v>75.31</v>
+        <v>111.3</v>
       </c>
       <c r="F25" t="n">
-        <v>60.63</v>
+        <v>83.97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[4, 4, 2, 1, 8]</t>
+          <t>[0, 6, 0, 7, 1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1048,526 +1048,526 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9738605254014545</v>
+        <v>0.980696845201699</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9738605254014545</v>
+        <v>0.980696845201699</v>
       </c>
       <c r="E26" t="n">
-        <v>106.44</v>
+        <v>106.96</v>
       </c>
       <c r="F26" t="n">
-        <v>88.06999999999999</v>
+        <v>89.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[3, 4, 1, 3, 6]</t>
+          <t>[3, 4, 4, 8, 9]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9754017591902626</v>
+        <v>0.9415179508974608</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9754017591902626</v>
+        <v>0.9415179508974608</v>
       </c>
       <c r="E27" t="n">
-        <v>98.03999999999999</v>
+        <v>102.64</v>
       </c>
       <c r="F27" t="n">
-        <v>78.21000000000001</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[7, 7, 1, 3, 4]</t>
+          <t>[6, 7, 5, 2, 5]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.992439109841606</v>
+        <v>0.9479347198205028</v>
       </c>
       <c r="D28" t="n">
-        <v>0.992439109841606</v>
+        <v>0.9479347198205028</v>
       </c>
       <c r="E28" t="n">
-        <v>115.33</v>
+        <v>115.82</v>
       </c>
       <c r="F28" t="n">
-        <v>99.07000000000001</v>
+        <v>77.94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[9, 2, 3, 6, 4]</t>
+          <t>[9, 7, 2, 9, 3]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9701634197779562</v>
+        <v>0.9417549377571565</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9701634197779562</v>
+        <v>0.9417549377571565</v>
       </c>
       <c r="E29" t="n">
-        <v>104.61</v>
+        <v>118</v>
       </c>
       <c r="F29" t="n">
-        <v>82.06999999999999</v>
+        <v>83.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[5, 1, 3, 6, 0]</t>
+          <t>[4, 4, 2, 6, 9]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9746290026671346</v>
+        <v>0.9456352247975426</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9746290026671346</v>
+        <v>0.9456352247975426</v>
       </c>
       <c r="E30" t="n">
-        <v>115.8</v>
+        <v>108.66</v>
       </c>
       <c r="F30" t="n">
-        <v>98.41999999999999</v>
+        <v>67.72999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[6, 0, 8, 3, 9]</t>
+          <t>[4, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9533579022383519</v>
+        <v>0.9702747245776149</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9533579022383519</v>
+        <v>0.9702747245776149</v>
       </c>
       <c r="E31" t="n">
-        <v>114.26</v>
+        <v>119.55</v>
       </c>
       <c r="F31" t="n">
-        <v>86.25</v>
+        <v>77.57000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[8, 2, 5, 7, 8]</t>
+          <t>[4, 1, 9, 6, 5]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9432108005664485</v>
+        <v>0.9698036023241858</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9432108005664485</v>
+        <v>0.9698036023241858</v>
       </c>
       <c r="E32" t="n">
-        <v>86.52</v>
+        <v>118.76</v>
       </c>
       <c r="F32" t="n">
-        <v>71.07000000000001</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[3, 6, 9, 7, 9]</t>
+          <t>[0, 9, 1, 5, 6]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.96406053362297</v>
+        <v>0.9535668574858013</v>
       </c>
       <c r="D33" t="n">
-        <v>0.96406053362297</v>
+        <v>0.9535668574858013</v>
       </c>
       <c r="E33" t="n">
-        <v>95.31</v>
+        <v>111.55</v>
       </c>
       <c r="F33" t="n">
-        <v>78.98</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[6, 7, 1, 1, 4]</t>
+          <t>[3, 6, 7, 1, 0]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.958937318815045</v>
+        <v>0.9678136070543403</v>
       </c>
       <c r="D34" t="n">
-        <v>0.958937318815045</v>
+        <v>0.9678136070543403</v>
       </c>
       <c r="E34" t="n">
-        <v>111.88</v>
+        <v>114.71</v>
       </c>
       <c r="F34" t="n">
-        <v>95.21000000000001</v>
+        <v>82.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[0, 8, 7, 2, 1]</t>
+          <t>[2, 5, 2, 0, 8]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9729446324561078</v>
+        <v>0.9749998031648645</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9729446324561078</v>
+        <v>0.9749998031648645</v>
       </c>
       <c r="E35" t="n">
-        <v>116.24</v>
+        <v>117.77</v>
       </c>
       <c r="F35" t="n">
-        <v>97.12</v>
+        <v>68.23999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[6, 4, 7, 0, 4]</t>
+          <t>[8, 7, 2, 7, 8]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9778277450032047</v>
+        <v>0.9662229255296637</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9778277450032047</v>
+        <v>0.9662229255296637</v>
       </c>
       <c r="E36" t="n">
-        <v>119.94</v>
+        <v>117.5</v>
       </c>
       <c r="F36" t="n">
-        <v>94.57999999999998</v>
+        <v>88.71000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[4, 3, 5, 8, 5]</t>
+          <t>[5, 6, 4, 7, 3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9907738230222226</v>
+        <v>0.9386317293111125</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9907738230222226</v>
+        <v>0.9386317293111125</v>
       </c>
       <c r="E37" t="n">
-        <v>111.64</v>
+        <v>94.80000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>96.22</v>
+        <v>63.54000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[5, 9, 5, 3, 8]</t>
+          <t>[6, 5, 8, 5, 1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9871748674714552</v>
+        <v>0.9614967969704677</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9871748674714552</v>
+        <v>0.9614967969704677</v>
       </c>
       <c r="E38" t="n">
-        <v>108.1</v>
+        <v>96.89000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>96.03999999999999</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 5, 2]</t>
+          <t>[5, 4, 7, 6, 7]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9769179972525125</v>
+        <v>0.9620275338246832</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9769179972525125</v>
+        <v>0.9620275338246832</v>
       </c>
       <c r="E39" t="n">
-        <v>117.39</v>
+        <v>110.55</v>
       </c>
       <c r="F39" t="n">
-        <v>97.61</v>
+        <v>80.44000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[7, 1, 5, 8, 0]</t>
+          <t>[0, 3, 7, 2, 1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9746413379036526</v>
+        <v>0.9760613752685114</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9746413379036526</v>
+        <v>0.9760613752685114</v>
       </c>
       <c r="E40" t="n">
-        <v>108.38</v>
+        <v>119.55</v>
       </c>
       <c r="F40" t="n">
-        <v>94.68000000000001</v>
+        <v>79.14999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[5, 1, 9, 3, 7]</t>
+          <t>[1, 9, 2, 1, 1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9669377267192327</v>
+        <v>0.9707345259274957</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9669377267192327</v>
+        <v>0.9707345259274957</v>
       </c>
       <c r="E41" t="n">
-        <v>105.96</v>
+        <v>113.54</v>
       </c>
       <c r="F41" t="n">
-        <v>91.42999999999999</v>
+        <v>86.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[1, 6, 5, 6, 3]</t>
+          <t>[4, 5, 9, 2, 5]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.989901922187825</v>
+        <v>0.9671657223881569</v>
       </c>
       <c r="D42" t="n">
-        <v>0.989901922187825</v>
+        <v>0.9671657223881569</v>
       </c>
       <c r="E42" t="n">
-        <v>108.22</v>
+        <v>118.1</v>
       </c>
       <c r="F42" t="n">
-        <v>97.7</v>
+        <v>75.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[7, 3, 7, 3, 4]</t>
+          <t>[5, 6, 0, 5, 7]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 3, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9916443491780622</v>
+        <v>0.9887868524644152</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9916443491780622</v>
+        <v>0.9887868524644152</v>
       </c>
       <c r="E43" t="n">
-        <v>117.12</v>
+        <v>113.36</v>
       </c>
       <c r="F43" t="n">
-        <v>93.58000000000001</v>
+        <v>84.56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[9, 7, 3, 4, 5]</t>
+          <t>[4, 7, 9, 4, 0]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9495690255351407</v>
+        <v>0.9647684450106931</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9495690255351407</v>
+        <v>0.9647684450106931</v>
       </c>
       <c r="E44" t="n">
-        <v>101.44</v>
+        <v>118.74</v>
       </c>
       <c r="F44" t="n">
-        <v>95.02</v>
+        <v>94.61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[3, 2, 3, 4, 5]</t>
+          <t>[7, 9, 2, 8, 8]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 2]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9760982637295897</v>
+        <v>0.9714938687890341</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9760982637295897</v>
+        <v>0.9714938687890341</v>
       </c>
       <c r="E45" t="n">
-        <v>109.02</v>
+        <v>113.61</v>
       </c>
       <c r="F45" t="n">
-        <v>93.53999999999999</v>
+        <v>95.51999999999998</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[3, 4, 6, 9, 0]</t>
+          <t>[7, 8, 2, 5, 7]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9662345135450295</v>
+        <v>0.9904787361897539</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9662345135450295</v>
+        <v>0.9904787361897539</v>
       </c>
       <c r="E46" t="n">
-        <v>108.29</v>
+        <v>117.8</v>
       </c>
       <c r="F46" t="n">
-        <v>83.38999999999999</v>
+        <v>82.63000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[1, 7, 9, 5, 4]</t>
+          <t>[8, 6, 7, 4, 7]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.971694779045611</v>
+        <v>0.9606584770273383</v>
       </c>
       <c r="D47" t="n">
-        <v>0.971694779045611</v>
+        <v>0.9606584770273383</v>
       </c>
       <c r="E47" t="n">
-        <v>106.26</v>
+        <v>110.4</v>
       </c>
       <c r="F47" t="n">
-        <v>97.54000000000001</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[4, 7, 3, 1, 0]</t>
+          <t>[2, 5, 3, 8, 7]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1576,88 +1576,88 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.973042648375998</v>
+        <v>0.9628898029900651</v>
       </c>
       <c r="D48" t="n">
-        <v>0.973042648375998</v>
+        <v>0.9628898029900651</v>
       </c>
       <c r="E48" t="n">
-        <v>101.03</v>
+        <v>111.07</v>
       </c>
       <c r="F48" t="n">
-        <v>80.78</v>
+        <v>69.45999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[0, 7, 5, 6, 7]</t>
+          <t>[0, 5, 6, 5, 4]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9916807893622301</v>
+        <v>0.9722541797101987</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9916807893622301</v>
+        <v>0.9722541797101987</v>
       </c>
       <c r="E49" t="n">
-        <v>105.34</v>
+        <v>108.23</v>
       </c>
       <c r="F49" t="n">
-        <v>95.33999999999999</v>
+        <v>73.44999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[5, 7, 7, 9, 3]</t>
+          <t>[6, 7, 9, 5, 6]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9438376574923658</v>
+        <v>0.9601803005119444</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9438376574923658</v>
+        <v>0.9601803005119444</v>
       </c>
       <c r="E50" t="n">
-        <v>103.08</v>
+        <v>105.74</v>
       </c>
       <c r="F50" t="n">
-        <v>87.46000000000001</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[8, 7, 1, 5, 9]</t>
+          <t>[6, 6, 8, 7, 3]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9684210436607379</v>
+        <v>0.9605174005756175</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9684210436607379</v>
+        <v>0.9605174005756175</v>
       </c>
       <c r="E51" t="n">
-        <v>92.31999999999999</v>
+        <v>105.07</v>
       </c>
       <c r="F51" t="n">
-        <v>82.45999999999999</v>
+        <v>79.75</v>
       </c>
     </row>
   </sheetData>
